--- a/data/AllInventoryData.xlsx
+++ b/data/AllInventoryData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a1dad5ec87e9ff/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ritik\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{433AA668-6AA3-41DC-8D40-4511B613C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE52106D-6179-4717-B374-D807C4C5151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FBF98F23-471D-48CC-8844-FA26C86842B3}"/>
   </bookViews>
